--- a/tests/fixtures/02_product_catalog/pattern.xlsx
+++ b/tests/fixtures/02_product_catalog/pattern.xlsx
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>header.product</t>
+          <t>col_product</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,12 +458,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>header.sku</t>
+          <t>col_sku</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -480,12 +480,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>header.qty</t>
+          <t>col_qty</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -502,12 +502,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>header.price</t>
+          <t>col_price</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>header.product</t>
+          <t>col_product</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>header.sku</t>
+          <t>col_sku</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>header.qty</t>
+          <t>col_qty</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>header.price</t>
+          <t>col_price</t>
         </is>
       </c>
     </row>
